--- a/output/laminas_comunales/comunal_p_aps_a_2020_coquimbo.xlsx
+++ b/output/laminas_comunales/comunal_p_aps_a_2020_coquimbo.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C316"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,121 +375,121 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vicuña</t>
+          <t>Canela</t>
         </is>
       </c>
       <c r="C2">
-        <v>53.86148452758789</v>
+        <v>132393.375</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Salamanca</t>
+          <t>Río Hurtado</t>
         </is>
       </c>
       <c r="C3">
-        <v>53.67975997924805</v>
+        <v>125788.578125</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Andacollo</t>
+          <t>Canela</t>
         </is>
       </c>
       <c r="C4">
-        <v>53.21307754516602</v>
+        <v>125096.96875</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Los Vilos</t>
+          <t>Monte Patria</t>
         </is>
       </c>
       <c r="C5">
-        <v>51.5033073425293</v>
+        <v>124567.625</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Illapel</t>
+          <t>Canela</t>
         </is>
       </c>
       <c r="C6">
-        <v>51.19754409790039</v>
+        <v>124477.4765625</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Monte Patria</t>
+          <t>La Higuera</t>
         </is>
       </c>
       <c r="C7">
-        <v>51.00671005249023</v>
+        <v>124131.0390625</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Combarbalá</t>
+          <t>Canela</t>
         </is>
       </c>
       <c r="C8">
-        <v>49.24623107910156</v>
+        <v>123334.4453125</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4301</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ovalle</t>
+          <t>Monte Patria</t>
         </is>
       </c>
       <c r="C9">
-        <v>48.88166046142578</v>
+        <v>122583.53125</v>
       </c>
     </row>
     <row r="10">
@@ -504,82 +504,4597 @@
         </is>
       </c>
       <c r="C10">
-        <v>48.7931022644043</v>
+        <v>122184.2578125</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Canela</t>
         </is>
       </c>
       <c r="C11">
-        <v>48.71419525146484</v>
+        <v>121453.890625</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4202</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Canela</t>
+          <t>La Higuera</t>
         </is>
       </c>
       <c r="C12">
-        <v>46.7265739440918</v>
+        <v>121196.9375</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Punitaqui</t>
+          <t>La Higuera</t>
         </is>
       </c>
       <c r="C13">
-        <v>45.64777374267578</v>
+        <v>120913.3828125</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>La Higuera</t>
         </is>
       </c>
       <c r="C14">
-        <v>43.3285026550293</v>
+        <v>120681.5390625</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>120478.9140625</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>120317.4375</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>120114.140625</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>119810</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>119523.625</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>119230.953125</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>4305</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Río Hurtado</t>
         </is>
       </c>
-      <c r="C15">
+      <c r="C21">
+        <v>118662.7734375</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>117945.1015625</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>117908.9453125</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>117732.3671875</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>117299.015625</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>117298.6484375</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>116999.2578125</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>116880.3515625</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>116558.5703125</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>116341.6953125</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>116341.390625</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>116317.796875</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>116159.890625</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>116037.5625</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>115851.7734375</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>115680.8359375</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>115580.1015625</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>115565.28125</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>115512.4140625</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>115342.2734375</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>115026.6640625</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>114596.859375</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>114580.7109375</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>114514.1796875</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>114421.484375</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>114324.6328125</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>114306.5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>114197.4921875</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>114046.2890625</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>113723.640625</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>112989.640625</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>112955.3125</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>112870.8125</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>112836.1640625</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>112616.875</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>112530.8671875</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>112360.25</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>112274.703125</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>112246.828125</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>112137.296875</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>111184.28125</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>111057.6328125</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>110701.375</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>110665.046875</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>110632.796875</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>110286.78125</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>110138.0703125</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>109838.0546875</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>109702.34375</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>109577.109375</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>109388.3203125</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>109332.71875</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>109317.0390625</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>109253.3671875</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>108898.78125</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>108828.2890625</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>108690.546875</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>108576.6640625</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>108447.7578125</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>107549.328125</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>107503.7421875</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>107431.28125</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>107142.3671875</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>106991.6484375</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>106905.4375</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>106887.9375</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>106544.984375</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>106454.6953125</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>105714.4453125</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>105063.1640625</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>104878.7890625</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>104872.1875</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>104810.8203125</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>104744.9609375</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>104719.640625</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>102912.3125</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>102714.2890625</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>102240.1328125</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>102179.0390625</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>102125.9453125</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>100960.40625</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>100687.6015625</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>99528.4453125</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>98790.4453125</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>97827.4375</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>97285.5</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>63.82022476196289</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>58.82352828979492</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>57.30801010131836</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>57.07171249389648</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>56.48936080932617</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>56.30252075195313</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>55.87334060668945</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>55.833984375</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>55.74468231201172</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>55.28925704956055</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>54.72906494140625</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>54.05790328979492</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>53.86148452758789</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>53.72208404541016</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>53.67975997924805</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>53.66300201416016</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>53.37490844726563</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>53.26370620727539</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>53.22034072875977</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>53.21307754516602</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>52.97378921508789</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>52.84090805053711</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>52.70291519165039</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>52.49849319458008</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>52.49520111083984</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>51.85185241699219</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>51.76470565795898</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>51.73271942138672</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>51.5033073425293</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>51.49330520629883</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>51.46341323852539</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>51.19754409790039</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>51.00671005249023</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>50.87719345092773</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>50.79787063598633</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>50.72000122070313</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>50.68153762817383</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>50.5105094909668</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>50.46604537963867</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>50.40871810913086</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>50.18292617797852</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>50.10991668701172</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>49.90234375</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>49.86449813842773</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>49.80544662475586</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>49.69939804077148</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>49.64028930664063</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>49.52815246582031</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>49.52229309082031</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>49.52107238769531</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>49.52038192749023</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>49.40218734741211</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>49.24623107910156</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>49.12203598022461</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>48.88166046142578</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>48.7931022644043</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>48.71419525146484</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>48.6216926574707</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>48.44835662841797</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>48.41530227661133</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>48.34355926513672</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>48.15340805053711</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>47.98090362548828</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>47.9764404296875</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>47.96656799316406</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>47.68627548217773</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>47.3684196472168</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>47.34998321533203</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>47.1172981262207</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>46.7265739440918</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>46.61654281616211</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>46.61558151245117</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>46.51763153076172</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>46.402587890625</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>46.28665161132813</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>45.94609069824219</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>45.91268157958984</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>45.89800262451172</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>45.64777374267578</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>45.55084609985352</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>45.39497756958008</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>45.35073471069336</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>45.2983283996582</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>45.18760299682617</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>45.08404159545898</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>44.78776168823242</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>44.44444274902344</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>44.36090087890625</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>44.36090087890625</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>44.21052551269531</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>43.79947280883789</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>43.64406967163086</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>43.42342376708984</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>43.42105102539063</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>43.3285026550293</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>43.26107406616211</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>43.2465934753418</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>43.23968505859375</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>43.03534317016602</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>42.57425689697266</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C208">
+        <v>42.55455780029297</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>42.5101203918457</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>42.20562362670898</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>41.61701965332031</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C212">
         <v>41.3450927734375</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>40.44944000244141</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C214">
+        <v>40.25531768798828</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C215">
+        <v>39.89966583251953</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C216">
+        <v>39.12568283081055</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C217">
+        <v>39.01108169555664</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C218">
+        <v>38.8505744934082</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C219">
+        <v>37.64044952392578</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C220">
+        <v>36.9523811340332</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C221">
+        <v>36.63366317749023</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C222">
+        <v>36.32437515258789</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C223">
+        <v>36.270751953125</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C224">
+        <v>35.17089462280273</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C225">
+        <v>34.87804794311523</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C226">
+        <v>34.46808624267578</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C227">
+        <v>34.11764526367188</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C228">
+        <v>33.82157135009766</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C229">
+        <v>33.55932235717773</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C230">
+        <v>33.10344696044922</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C231">
+        <v>32.96296310424805</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C232">
+        <v>32.64033126831055</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C233">
+        <v>32.6315803527832</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C234">
+        <v>32.55813980102539</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C235">
+        <v>32.34042739868164</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C236">
+        <v>30.99870300292969</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C237">
+        <v>30.55759429931641</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C238">
+        <v>30.32581520080566</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C239">
+        <v>29.85318183898926</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C240">
+        <v>29.7508544921875</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C241">
+        <v>29.52127647399902</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C242">
+        <v>29.37915802001953</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C243">
+        <v>29.33333396911621</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C244">
+        <v>29.00287628173828</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C245">
+        <v>28.89825439453125</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C246">
+        <v>27.73006057739258</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C247">
+        <v>27.4974250793457</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C248">
+        <v>27.44063377380371</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C249">
+        <v>27.1929817199707</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C250">
+        <v>26.45450019836426</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C251">
+        <v>26.24661827087402</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C252">
+        <v>25.99199104309082</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C253">
+        <v>25.97365188598633</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C254">
+        <v>25.82253265380859</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C255">
+        <v>25.63694190979004</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C256">
+        <v>25.20242881774902</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C257">
+        <v>25.10811424255371</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C258">
+        <v>24.80079650878906</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C259">
+        <v>24.64986038208008</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C260">
+        <v>24.21875</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C261">
+        <v>23.90804672241211</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C262">
+        <v>23.54968452453613</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C263">
+        <v>23.50119972229004</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C264">
+        <v>23.50051116943359</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C265">
+        <v>23.46590995788574</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C266">
+        <v>23.44913101196289</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C267">
+        <v>23.37524032592773</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C268">
+        <v>23.37254905700684</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C269">
+        <v>23.34975433349609</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C270">
+        <v>23.27119636535645</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C271">
+        <v>22.83669281005859</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C272">
+        <v>22.75992965698242</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C273">
+        <v>22.7170238494873</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C274">
+        <v>22.66401672363281</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C275">
+        <v>22.46077537536621</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C276">
+        <v>22.23999977111816</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C277">
+        <v>21.80451202392578</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C278">
+        <v>21.80180168151855</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C279">
+        <v>21.69540214538574</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C280">
+        <v>20.67415809631348</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C281">
+        <v>20.57220649719238</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C282">
+        <v>20.1786060333252</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C283">
+        <v>19.81452560424805</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C284">
+        <v>19.7389030456543</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C285">
+        <v>19.58438301086426</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C286">
+        <v>19.57247734069824</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C287">
+        <v>19.29182434082031</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C288">
+        <v>18.9233283996582</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C289">
+        <v>18.91673469543457</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C290">
+        <v>18.07722663879395</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C291">
+        <v>18.0656566619873</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C292">
+        <v>17.75067710876465</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C293">
+        <v>17.65765762329102</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C294">
+        <v>17.6136360168457</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C295">
+        <v>17.42623710632324</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C296">
+        <v>17.27392387390137</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C297">
+        <v>17.25904273986816</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C298">
+        <v>17.14001083374023</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C299">
+        <v>16.61157035827637</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C300">
+        <v>16.08870315551758</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C301">
+        <v>15.75091552734375</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C302">
+        <v>15.02357482910156</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C303">
+        <v>14.70888614654541</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C304">
+        <v>14.6541109085083</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C305">
+        <v>14.590087890625</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C306">
+        <v>14.29439735412598</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C307">
+        <v>14.04203510284424</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C308">
+        <v>13.93034839630127</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C309">
+        <v>13.19509887695313</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C310">
+        <v>12.3996524810791</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C311">
+        <v>11.51616477966309</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C312">
+        <v>10.78629016876221</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C313">
+        <v>10.72826957702637</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C314">
+        <v>9.693759918212891</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C315">
+        <v>9.472421646118164</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C316">
+        <v>7.97953987121582</v>
       </c>
     </row>
   </sheetData>
